--- a/data/revolutionrace_trends_monthly.xlsx
+++ b/data/revolutionrace_trends_monthly.xlsx
@@ -517,7 +517,7 @@
         <v>43799</v>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -525,7 +525,7 @@
         <v>43830</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -533,7 +533,7 @@
         <v>43861</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +541,7 @@
         <v>43890</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>43951</v>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>44012</v>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>44043</v>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -589,7 +589,7 @@
         <v>44074</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>44135</v>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>44165</v>
       </c>
       <c r="B24" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>44196</v>
       </c>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>44227</v>
       </c>
       <c r="B26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>44255</v>
       </c>
       <c r="B27" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>44347</v>
       </c>
       <c r="B30" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
@@ -669,7 +669,7 @@
         <v>44377</v>
       </c>
       <c r="B31" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32">
@@ -685,7 +685,7 @@
         <v>44439</v>
       </c>
       <c r="B33" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>44469</v>
       </c>
       <c r="B34" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>44500</v>
       </c>
       <c r="B35" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
@@ -733,7 +733,7 @@
         <v>44620</v>
       </c>
       <c r="B39" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>44651</v>
       </c>
       <c r="B40" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
@@ -757,7 +757,7 @@
         <v>44712</v>
       </c>
       <c r="B42" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>44742</v>
       </c>
       <c r="B43" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>44773</v>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45">
@@ -797,7 +797,7 @@
         <v>44865</v>
       </c>
       <c r="B47" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>44895</v>
       </c>
       <c r="B48" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>44926</v>
       </c>
       <c r="B49" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>44957</v>
       </c>
       <c r="B50" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>44985</v>
       </c>
       <c r="B51" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>45016</v>
       </c>
       <c r="B52" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53">
@@ -877,7 +877,7 @@
         <v>45169</v>
       </c>
       <c r="B57" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,7 @@
         <v>45199</v>
       </c>
       <c r="B58" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59">
@@ -893,7 +893,7 @@
         <v>45230</v>
       </c>
       <c r="B59" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60">
@@ -917,7 +917,7 @@
         <v>45322</v>
       </c>
       <c r="B62" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
@@ -925,7 +925,7 @@
         <v>45351</v>
       </c>
       <c r="B63" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64">
@@ -933,7 +933,7 @@
         <v>45382</v>
       </c>
       <c r="B64" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
@@ -949,7 +949,7 @@
         <v>45443</v>
       </c>
       <c r="B66" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67">
@@ -957,7 +957,7 @@
         <v>45473</v>
       </c>
       <c r="B67" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68">
@@ -973,7 +973,7 @@
         <v>45535</v>
       </c>
       <c r="B69" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="70">
@@ -981,7 +981,7 @@
         <v>45565</v>
       </c>
       <c r="B70" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71">
@@ -997,7 +997,7 @@
         <v>45626</v>
       </c>
       <c r="B72" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73">
@@ -1005,7 +1005,7 @@
         <v>45657</v>
       </c>
       <c r="B73" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74">
@@ -1013,7 +1013,7 @@
         <v>45688</v>
       </c>
       <c r="B74" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75">
@@ -1021,7 +1021,7 @@
         <v>45716</v>
       </c>
       <c r="B75" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76">
@@ -1029,7 +1029,7 @@
         <v>45747</v>
       </c>
       <c r="B76" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77">
@@ -1037,7 +1037,7 @@
         <v>45777</v>
       </c>
       <c r="B77" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78">
@@ -1045,7 +1045,7 @@
         <v>45808</v>
       </c>
       <c r="B78" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79">
@@ -1053,7 +1053,7 @@
         <v>45838</v>
       </c>
       <c r="B79" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -1061,7 +1061,7 @@
         <v>45869</v>
       </c>
       <c r="B80" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81">
@@ -1069,7 +1069,7 @@
         <v>45900</v>
       </c>
       <c r="B81" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82">
@@ -1085,7 +1085,7 @@
         <v>45961</v>
       </c>
       <c r="B83" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84">
@@ -1101,7 +1101,7 @@
         <v>46022</v>
       </c>
       <c r="B85" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="86">
@@ -1109,7 +1109,7 @@
         <v>46053</v>
       </c>
       <c r="B86" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="87">
@@ -1117,7 +1117,7 @@
         <v>46081</v>
       </c>
       <c r="B87" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="88">
@@ -1125,7 +1125,7 @@
         <v>46112</v>
       </c>
       <c r="B88" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/data/revolutionrace_trends_monthly.xlsx
+++ b/data/revolutionrace_trends_monthly.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,7 +525,7 @@
         <v>43830</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>43890</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -573,7 +573,7 @@
         <v>44012</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>44043</v>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -605,7 +605,7 @@
         <v>44135</v>
       </c>
       <c r="B23" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>44165</v>
       </c>
       <c r="B24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>44196</v>
       </c>
       <c r="B25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>44227</v>
       </c>
       <c r="B26" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>44255</v>
       </c>
       <c r="B27" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
@@ -645,7 +645,7 @@
         <v>44286</v>
       </c>
       <c r="B28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
@@ -653,7 +653,7 @@
         <v>44316</v>
       </c>
       <c r="B29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30">
@@ -661,7 +661,7 @@
         <v>44347</v>
       </c>
       <c r="B30" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
@@ -677,7 +677,7 @@
         <v>44408</v>
       </c>
       <c r="B32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -685,7 +685,7 @@
         <v>44439</v>
       </c>
       <c r="B33" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>44469</v>
       </c>
       <c r="B34" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>44500</v>
       </c>
       <c r="B35" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36">
@@ -709,7 +709,7 @@
         <v>44530</v>
       </c>
       <c r="B36" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
@@ -717,7 +717,7 @@
         <v>44561</v>
       </c>
       <c r="B37" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -725,7 +725,7 @@
         <v>44592</v>
       </c>
       <c r="B38" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39">
@@ -733,7 +733,7 @@
         <v>44620</v>
       </c>
       <c r="B39" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>44651</v>
       </c>
       <c r="B40" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41">
@@ -749,7 +749,7 @@
         <v>44681</v>
       </c>
       <c r="B41" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
@@ -757,7 +757,7 @@
         <v>44712</v>
       </c>
       <c r="B42" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>44742</v>
       </c>
       <c r="B43" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>44773</v>
       </c>
       <c r="B44" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">
@@ -781,7 +781,7 @@
         <v>44804</v>
       </c>
       <c r="B45" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46">
@@ -789,7 +789,7 @@
         <v>44834</v>
       </c>
       <c r="B46" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
@@ -797,7 +797,7 @@
         <v>44865</v>
       </c>
       <c r="B47" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>44895</v>
       </c>
       <c r="B48" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>44926</v>
       </c>
       <c r="B49" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>44957</v>
       </c>
       <c r="B50" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>44985</v>
       </c>
       <c r="B51" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>45016</v>
       </c>
       <c r="B52" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
@@ -845,7 +845,7 @@
         <v>45046</v>
       </c>
       <c r="B53" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54">
@@ -853,7 +853,7 @@
         <v>45077</v>
       </c>
       <c r="B54" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
@@ -861,7 +861,7 @@
         <v>45107</v>
       </c>
       <c r="B55" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56">
@@ -869,7 +869,7 @@
         <v>45138</v>
       </c>
       <c r="B56" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
@@ -877,7 +877,7 @@
         <v>45169</v>
       </c>
       <c r="B57" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,7 @@
         <v>45199</v>
       </c>
       <c r="B58" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59">
@@ -893,7 +893,7 @@
         <v>45230</v>
       </c>
       <c r="B59" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60">
@@ -901,7 +901,7 @@
         <v>45260</v>
       </c>
       <c r="B60" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61">
@@ -909,7 +909,7 @@
         <v>45291</v>
       </c>
       <c r="B61" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62">
@@ -917,7 +917,7 @@
         <v>45322</v>
       </c>
       <c r="B62" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63">
@@ -925,7 +925,7 @@
         <v>45351</v>
       </c>
       <c r="B63" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64">
@@ -933,7 +933,7 @@
         <v>45382</v>
       </c>
       <c r="B64" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">
@@ -941,7 +941,7 @@
         <v>45412</v>
       </c>
       <c r="B65" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66">
@@ -949,7 +949,7 @@
         <v>45443</v>
       </c>
       <c r="B66" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67">
@@ -965,7 +965,7 @@
         <v>45504</v>
       </c>
       <c r="B68" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69">
@@ -973,7 +973,7 @@
         <v>45535</v>
       </c>
       <c r="B69" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70">
@@ -981,7 +981,7 @@
         <v>45565</v>
       </c>
       <c r="B70" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71">
@@ -989,7 +989,7 @@
         <v>45596</v>
       </c>
       <c r="B71" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72">
@@ -997,7 +997,7 @@
         <v>45626</v>
       </c>
       <c r="B72" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73">
@@ -1005,7 +1005,7 @@
         <v>45657</v>
       </c>
       <c r="B73" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74">
@@ -1013,7 +1013,7 @@
         <v>45688</v>
       </c>
       <c r="B74" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75">
@@ -1021,7 +1021,7 @@
         <v>45716</v>
       </c>
       <c r="B75" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76">
@@ -1029,7 +1029,7 @@
         <v>45747</v>
       </c>
       <c r="B76" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77">
@@ -1037,7 +1037,7 @@
         <v>45777</v>
       </c>
       <c r="B77" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78">
@@ -1045,7 +1045,7 @@
         <v>45808</v>
       </c>
       <c r="B78" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79">
@@ -1053,7 +1053,7 @@
         <v>45838</v>
       </c>
       <c r="B79" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80">
@@ -1061,7 +1061,7 @@
         <v>45869</v>
       </c>
       <c r="B80" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81">
@@ -1069,7 +1069,7 @@
         <v>45900</v>
       </c>
       <c r="B81" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82">
@@ -1077,7 +1077,7 @@
         <v>45930</v>
       </c>
       <c r="B82" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83">
@@ -1085,7 +1085,7 @@
         <v>45961</v>
       </c>
       <c r="B83" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84">
@@ -1101,7 +1101,7 @@
         <v>46022</v>
       </c>
       <c r="B85" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86">
@@ -1109,7 +1109,7 @@
         <v>46053</v>
       </c>
       <c r="B86" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87">
@@ -1117,7 +1117,7 @@
         <v>46081</v>
       </c>
       <c r="B87" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88">
@@ -1125,7 +1125,15 @@
         <v>46112</v>
       </c>
       <c r="B88" t="n">
-        <v>55</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B89" t="n">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data/revolutionrace_trends_monthly.xlsx
+++ b/data/revolutionrace_trends_monthly.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,23 +429,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>RevolutionRace</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B2" t="n">
@@ -441,7 +453,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B3" t="n">
@@ -449,7 +461,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B4" t="n">
@@ -457,7 +469,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B5" t="n">
@@ -465,7 +477,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B6" t="n">
@@ -473,7 +485,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B7" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B8" t="n">
@@ -489,7 +501,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B9" t="n">
@@ -497,7 +509,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B10" t="n">
@@ -505,23 +517,23 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B13" t="n">
@@ -529,15 +541,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B15" t="n">
@@ -545,23 +557,23 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B18" t="n">
@@ -569,7 +581,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B19" t="n">
@@ -577,15 +589,15 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B21" t="n">
@@ -593,63 +605,63 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B22" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>44135</v>
+      </c>
+      <c r="B23" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>44135</v>
-      </c>
-      <c r="B23" t="n">
-        <v>35</v>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B24" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B27" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B28" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B29" t="n">
@@ -657,23 +669,23 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B30" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B31" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B32" t="n">
@@ -681,7 +693,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B33" t="n">
@@ -689,23 +701,23 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B34" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>44500</v>
+      </c>
+      <c r="B35" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="B35" t="n">
-        <v>46</v>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B36" t="n">
@@ -713,39 +725,39 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B37" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B38" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B39" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B40" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B41" t="n">
@@ -753,23 +765,23 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B42" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B43" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B44" t="n">
@@ -777,31 +789,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B45" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B46" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B47" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B48" t="n">
@@ -809,47 +821,47 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B49" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B50" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>44985</v>
+      </c>
+      <c r="B51" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B52" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45046</v>
+      </c>
+      <c r="B53" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>44985</v>
-      </c>
-      <c r="B51" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>45016</v>
-      </c>
-      <c r="B52" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>45046</v>
-      </c>
-      <c r="B53" t="n">
-        <v>48</v>
-      </c>
-    </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B54" t="n">
@@ -857,63 +869,63 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B55" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B56" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B57" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B58" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B59" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B60" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B61" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B62" t="n">
@@ -921,63 +933,63 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B63" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B64" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B65" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B66" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B67" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B68" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B69" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B70" t="n">
@@ -985,7 +997,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B71" t="n">
@@ -993,7 +1005,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B72" t="n">
@@ -1001,31 +1013,31 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B73" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B74" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B74" t="n">
-        <v>55</v>
-      </c>
-    </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B75" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B76" t="n">
@@ -1033,55 +1045,55 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B77" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B78" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B79" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B80" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B81" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B82" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B83" t="n">
@@ -1089,7 +1101,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B84" t="n">
@@ -1097,23 +1109,23 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B85" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B86" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B87" t="n">
@@ -1121,19 +1133,59 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B88" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B89" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B90" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B91" t="n">
         <v>33</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B92" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B93" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B94" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
